--- a/01_Thermal/B_results/four_annular_gp_analysis.xlsx
+++ b/01_Thermal/B_results/four_annular_gp_analysis.xlsx
@@ -484,16 +484,16 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>31.19237995989421</v>
+        <v>32.15591478812478</v>
       </c>
       <c r="E2" t="n">
-        <v>8.405837931999532</v>
+        <v>8.662984295797726</v>
       </c>
       <c r="F2" t="n">
-        <v>0.174229416394219</v>
+        <v>0.2027831479042894</v>
       </c>
       <c r="G2" t="n">
-        <v>129.3311386450848</v>
+        <v>175.1958677393621</v>
       </c>
       <c r="H2" t="n">
         <v>4260.495759386248</v>
@@ -512,16 +512,16 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>41.67785839010216</v>
+        <v>46.9964700435003</v>
       </c>
       <c r="E3" t="n">
-        <v>38.83296343140761</v>
+        <v>45.56542672268462</v>
       </c>
       <c r="F3" t="n">
-        <v>0.203686989493951</v>
+        <v>0.2300603569486</v>
       </c>
       <c r="G3" t="n">
-        <v>228.7207965947854</v>
+        <v>291.7847935990236</v>
       </c>
       <c r="H3" t="n">
         <v>5512.886817461289</v>
@@ -540,16 +540,16 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>38.88507412699893</v>
+        <v>40.95357411416045</v>
       </c>
       <c r="E4" t="n">
-        <v>23.11008878871879</v>
+        <v>24.67292331395973</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2675214516297924</v>
+        <v>0.2897078592162587</v>
       </c>
       <c r="G4" t="n">
-        <v>269.5737943337616</v>
+        <v>316.1411295747739</v>
       </c>
       <c r="H4" t="n">
         <v>3766.694924158668</v>
@@ -568,16 +568,16 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>36.07644754433866</v>
+        <v>39.44995219779057</v>
       </c>
       <c r="E5" t="n">
-        <v>14.42218933133137</v>
+        <v>17.5246898574569</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2558743131315485</v>
+        <v>0.2835759533018062</v>
       </c>
       <c r="G5" t="n">
-        <v>1121.88709776819</v>
+        <v>1377.953541140899</v>
       </c>
       <c r="H5" t="n">
         <v>17135.46024586531</v>
@@ -596,16 +596,16 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>38.42746639173841</v>
+        <v>45.37326094885551</v>
       </c>
       <c r="E6" t="n">
-        <v>17.55015233638559</v>
+        <v>24.34826070171258</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2428666304820695</v>
+        <v>0.2891279587672202</v>
       </c>
       <c r="G6" t="n">
-        <v>421.7820026772828</v>
+        <v>597.7678174596385</v>
       </c>
       <c r="H6" t="n">
         <v>7150.76242849565</v>
@@ -624,16 +624,16 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>25.31094092471963</v>
+        <v>30.93351431912789</v>
       </c>
       <c r="E7" t="n">
-        <v>7.285265314469828</v>
+        <v>11.24664981384535</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1978611168511706</v>
+        <v>0.2484151392453465</v>
       </c>
       <c r="G7" t="n">
-        <v>266.4722788843321</v>
+        <v>420.0367050450863</v>
       </c>
       <c r="H7" t="n">
         <v>6806.614016268456</v>
@@ -652,16 +652,16 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>25.89080603087181</v>
+        <v>33.91594803811211</v>
       </c>
       <c r="E8" t="n">
-        <v>6.706566329706177</v>
+        <v>11.76481362660272</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1763176733181888</v>
+        <v>0.2359866003422746</v>
       </c>
       <c r="G8" t="n">
-        <v>158.4779620088701</v>
+        <v>283.8911621744545</v>
       </c>
       <c r="H8" t="n">
         <v>5097.734174531417</v>
@@ -677,16 +677,16 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>237.4609733686638</v>
+        <v>269.7786344496716</v>
       </c>
       <c r="E9" t="n">
-        <v>116.3130634640189</v>
+        <v>143.7857483320596</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2284866245261445</v>
+        <v>0.2638759599380512</v>
       </c>
       <c r="G9" t="n">
-        <v>2596.245070912306</v>
+        <v>3462.771016733238</v>
       </c>
       <c r="H9" t="n">
         <v>49730.64836616704</v>
@@ -793,13 +793,13 @@
         <v>7.31</v>
       </c>
       <c r="I2" t="n">
-        <v>7.476525879302524</v>
+        <v>7.416313058692195</v>
       </c>
       <c r="J2" t="n">
         <v>4.5775</v>
       </c>
       <c r="K2" t="n">
-        <v>4.955840293758027</v>
+        <v>4.856366482755949</v>
       </c>
     </row>
     <row r="3">
@@ -832,13 +832,13 @@
         <v>6.66</v>
       </c>
       <c r="I3" t="n">
-        <v>6.676490420075641</v>
+        <v>6.798336326274096</v>
       </c>
       <c r="J3" t="n">
         <v>4.343333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>4.345822669377526</v>
+        <v>4.473445021820609</v>
       </c>
     </row>
     <row r="4">
@@ -871,13 +871,13 @@
         <v>6.83</v>
       </c>
       <c r="I4" t="n">
-        <v>6.795201677484906</v>
+        <v>6.753423150299891</v>
       </c>
       <c r="J4" t="n">
         <v>4.58</v>
       </c>
       <c r="K4" t="n">
-        <v>4.605500966190041</v>
+        <v>4.615513042454795</v>
       </c>
     </row>
     <row r="5">
@@ -910,13 +910,13 @@
         <v>6.283</v>
       </c>
       <c r="I5" t="n">
-        <v>6.229528105002706</v>
+        <v>6.227028752787276</v>
       </c>
       <c r="J5" t="n">
         <v>4.354333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>4.31842388956668</v>
+        <v>4.290787507922803</v>
       </c>
     </row>
     <row r="6">
@@ -945,13 +945,13 @@
         <v>27.083</v>
       </c>
       <c r="I6" t="n">
-        <v>27.17774608186578</v>
+        <v>27.19510128805346</v>
       </c>
       <c r="J6" t="n">
         <v>6.77075</v>
       </c>
       <c r="K6" t="n">
-        <v>6.794436520466444</v>
+        <v>6.798775322013364</v>
       </c>
     </row>
     <row r="7">
@@ -984,13 +984,13 @@
         <v>3.672</v>
       </c>
       <c r="I7" t="n">
-        <v>1.454324539545475</v>
+        <v>1.323562369201061</v>
       </c>
       <c r="J7" t="n">
         <v>2.5935</v>
       </c>
       <c r="K7" t="n">
-        <v>1.014472824890764</v>
+        <v>0.9151030632087672</v>
       </c>
     </row>
     <row r="8">
@@ -1023,13 +1023,13 @@
         <v>3.598</v>
       </c>
       <c r="I8" t="n">
-        <v>3.620393712614445</v>
+        <v>3.761384309891935</v>
       </c>
       <c r="J8" t="n">
         <v>2.582</v>
       </c>
       <c r="K8" t="n">
-        <v>2.634981338985013</v>
+        <v>2.750067219180605</v>
       </c>
     </row>
     <row r="9">
@@ -1062,13 +1062,13 @@
         <v>5.346</v>
       </c>
       <c r="I9" t="n">
-        <v>5.316685991761817</v>
+        <v>5.257965220609115</v>
       </c>
       <c r="J9" t="n">
         <v>3.14975</v>
       </c>
       <c r="K9" t="n">
-        <v>3.207948470404995</v>
+        <v>3.217130833092028</v>
       </c>
     </row>
     <row r="10">
@@ -1101,13 +1101,13 @@
         <v>3.606</v>
       </c>
       <c r="I10" t="n">
-        <v>3.700820289869358</v>
+        <v>3.648098002638617</v>
       </c>
       <c r="J10" t="n">
         <v>2.422666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>2.495864142110388</v>
+        <v>2.459096328123566</v>
       </c>
     </row>
     <row r="11">
@@ -1136,13 +1136,13 @@
         <v>16.222</v>
       </c>
       <c r="I11" t="n">
-        <v>14.0922245337911</v>
+        <v>13.99100990234073</v>
       </c>
       <c r="J11" t="n">
         <v>4.0555</v>
       </c>
       <c r="K11" t="n">
-        <v>3.523056133447774</v>
+        <v>3.497752475585183</v>
       </c>
     </row>
     <row r="12">
@@ -1175,13 +1175,13 @@
         <v>3.322</v>
       </c>
       <c r="I12" t="n">
-        <v>3.832138595743121</v>
+        <v>3.699765616822507</v>
       </c>
       <c r="J12" t="n">
         <v>1.951</v>
       </c>
       <c r="K12" t="n">
-        <v>2.202976714070778</v>
+        <v>2.128312593961923</v>
       </c>
     </row>
     <row r="13">
@@ -1214,13 +1214,13 @@
         <v>2.395</v>
       </c>
       <c r="I13" t="n">
-        <v>2.764601943485029</v>
+        <v>2.889844066610538</v>
       </c>
       <c r="J13" t="n">
         <v>1.944333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>1.868085068159688</v>
+        <v>1.963869488396502</v>
       </c>
     </row>
     <row r="14">
@@ -1253,13 +1253,13 @@
         <v>3.389</v>
       </c>
       <c r="I14" t="n">
-        <v>3.489512180831612</v>
+        <v>3.427444919494758</v>
       </c>
       <c r="J14" t="n">
         <v>2.5625</v>
       </c>
       <c r="K14" t="n">
-        <v>2.60080532037223</v>
+        <v>2.610225752755173</v>
       </c>
     </row>
     <row r="15">
@@ -1292,13 +1292,13 @@
         <v>2.734</v>
       </c>
       <c r="I15" t="n">
-        <v>2.769828841677883</v>
+        <v>2.700786222511771</v>
       </c>
       <c r="J15" t="n">
         <v>1.724</v>
       </c>
       <c r="K15" t="n">
-        <v>1.973411989177132</v>
+        <v>1.924181766351929</v>
       </c>
     </row>
     <row r="16">
@@ -1327,13 +1327,13 @@
         <v>11.84</v>
       </c>
       <c r="I16" t="n">
-        <v>12.85608156173765</v>
+        <v>12.71784082543957</v>
       </c>
       <c r="J16" t="n">
         <v>2.96</v>
       </c>
       <c r="K16" t="n">
-        <v>3.214020390434412</v>
+        <v>3.179460206359893</v>
       </c>
     </row>
     <row r="17">
@@ -1366,13 +1366,13 @@
         <v>2.997</v>
       </c>
       <c r="I17" t="n">
-        <v>1.914503382009573</v>
+        <v>1.930458679100686</v>
       </c>
       <c r="J17" t="n">
         <v>1.869</v>
       </c>
       <c r="K17" t="n">
-        <v>1.563130451942294</v>
+        <v>1.550853678705982</v>
       </c>
     </row>
     <row r="18">
@@ -1405,13 +1405,13 @@
         <v>2.182</v>
       </c>
       <c r="I18" t="n">
-        <v>2.138621754066468</v>
+        <v>2.286937626166762</v>
       </c>
       <c r="J18" t="n">
         <v>1.721</v>
       </c>
       <c r="K18" t="n">
-        <v>1.473130127962245</v>
+        <v>1.541724564113339</v>
       </c>
     </row>
     <row r="19">
@@ -1444,13 +1444,13 @@
         <v>3.611</v>
       </c>
       <c r="I19" t="n">
-        <v>3.378040641683027</v>
+        <v>3.385159081661953</v>
       </c>
       <c r="J19" t="n">
         <v>2.48</v>
       </c>
       <c r="K19" t="n">
-        <v>2.537362085778801</v>
+        <v>2.550563712863219</v>
       </c>
     </row>
     <row r="20">
@@ -1483,13 +1483,13 @@
         <v>3.509</v>
       </c>
       <c r="I20" t="n">
-        <v>3.207650276220559</v>
+        <v>3.113250383602602</v>
       </c>
       <c r="J20" t="n">
         <v>1.865</v>
       </c>
       <c r="K20" t="n">
-        <v>1.376418938160967</v>
+        <v>1.305412026478876</v>
       </c>
     </row>
     <row r="21">
@@ -1518,13 +1518,13 @@
         <v>12.299</v>
       </c>
       <c r="I21" t="n">
-        <v>10.63881605397963</v>
+        <v>10.715805770532</v>
       </c>
       <c r="J21" t="n">
         <v>3.07475</v>
       </c>
       <c r="K21" t="n">
-        <v>2.659704013494907</v>
+        <v>2.678951442633001</v>
       </c>
     </row>
     <row r="22">
@@ -1557,13 +1557,13 @@
         <v>2.954</v>
       </c>
       <c r="I22" t="n">
-        <v>2.860359307139779</v>
+        <v>2.961688890578897</v>
       </c>
       <c r="J22" t="n">
         <v>2.02725</v>
       </c>
       <c r="K22" t="n">
-        <v>2.284597290383344</v>
+        <v>2.356474878304748</v>
       </c>
     </row>
     <row r="23">
@@ -1596,13 +1596,13 @@
         <v>2.144</v>
       </c>
       <c r="I23" t="n">
-        <v>2.095830825515689</v>
+        <v>2.286964638287909</v>
       </c>
       <c r="J23" t="n">
         <v>1.503666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>1.696126347992624</v>
+        <v>1.771202297030148</v>
       </c>
     </row>
     <row r="24">
@@ -1635,13 +1635,13 @@
         <v>1.642</v>
       </c>
       <c r="I24" t="n">
-        <v>1.898045358770527</v>
+        <v>1.953045172332649</v>
       </c>
       <c r="J24" t="n">
         <v>1.25525</v>
       </c>
       <c r="K24" t="n">
-        <v>1.245369045413602</v>
+        <v>1.27316742326134</v>
       </c>
     </row>
     <row r="25">
@@ -1674,13 +1674,13 @@
         <v>2.317</v>
       </c>
       <c r="I25" t="n">
-        <v>2.466319910705371</v>
+        <v>2.337749728686704</v>
       </c>
       <c r="J25" t="n">
         <v>1.458</v>
       </c>
       <c r="K25" t="n">
-        <v>1.773853644440454</v>
+        <v>1.713087421550177</v>
       </c>
     </row>
     <row r="26">
@@ -1709,13 +1709,13 @@
         <v>9.057</v>
       </c>
       <c r="I26" t="n">
-        <v>9.320555402131367</v>
+        <v>9.539448429886159</v>
       </c>
       <c r="J26" t="n">
         <v>2.26425</v>
       </c>
       <c r="K26" t="n">
-        <v>2.330138850532842</v>
+        <v>2.38486210747154</v>
       </c>
     </row>
     <row r="27">
@@ -1748,13 +1748,13 @@
         <v>2.598</v>
       </c>
       <c r="I27" t="n">
-        <v>2.315683415185462</v>
+        <v>2.350909118958581</v>
       </c>
       <c r="J27" t="n">
         <v>1.5755</v>
       </c>
       <c r="K27" t="n">
-        <v>1.499646312284661</v>
+        <v>1.538046333577959</v>
       </c>
     </row>
     <row r="28">
@@ -1787,13 +1787,13 @@
         <v>1.464</v>
       </c>
       <c r="I28" t="n">
-        <v>1.781553234172052</v>
+        <v>1.9341557894611</v>
       </c>
       <c r="J28" t="n">
         <v>1.202666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>1.589607214387804</v>
+        <v>1.682781915305274</v>
       </c>
     </row>
     <row r="29">
@@ -1826,13 +1826,13 @@
         <v>1.402</v>
       </c>
       <c r="I29" t="n">
-        <v>1.501361145226651</v>
+        <v>1.527779455398029</v>
       </c>
       <c r="J29" t="n">
         <v>1.1765</v>
       </c>
       <c r="K29" t="n">
-        <v>1.189393563793123</v>
+        <v>1.264480872067553</v>
       </c>
     </row>
     <row r="30">
@@ -1865,13 +1865,13 @@
         <v>2.042</v>
       </c>
       <c r="I30" t="n">
-        <v>1.938648859068834</v>
+        <v>1.780429802997515</v>
       </c>
       <c r="J30" t="n">
         <v>1.508666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>1.312884299966541</v>
+        <v>1.17926914763693</v>
       </c>
     </row>
     <row r="31">
@@ -1900,13 +1900,13 @@
         <v>7.505999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>7.537246653652999</v>
+        <v>7.593274166815225</v>
       </c>
       <c r="J31" t="n">
         <v>1.8765</v>
       </c>
       <c r="K31" t="n">
-        <v>1.88431166341325</v>
+        <v>1.898318541703806</v>
       </c>
     </row>
     <row r="32">
@@ -1939,13 +1939,13 @@
         <v>2.347</v>
       </c>
       <c r="I32" t="n">
-        <v>1.702759629696386</v>
+        <v>1.613707493165421</v>
       </c>
       <c r="J32" t="n">
         <v>1.196</v>
       </c>
       <c r="K32" t="n">
-        <v>1.21864647595188</v>
+        <v>1.210334758106222</v>
       </c>
     </row>
     <row r="33">
@@ -1978,13 +1978,13 @@
         <v>1.6</v>
       </c>
       <c r="I33" t="n">
-        <v>1.29711322299346</v>
+        <v>1.490481394676311</v>
       </c>
       <c r="J33" t="n">
         <v>0.8406666666666668</v>
       </c>
       <c r="K33" t="n">
-        <v>0.996516763459641</v>
+        <v>1.069196562412963</v>
       </c>
     </row>
     <row r="34">
@@ -2017,13 +2017,13 @@
         <v>1.481</v>
       </c>
       <c r="I34" t="n">
-        <v>1.698462088683069</v>
+        <v>1.682635643035865</v>
       </c>
       <c r="J34" t="n">
         <v>0.7117500000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8214108862962035</v>
+        <v>0.9073546471057639</v>
       </c>
     </row>
     <row r="35">
@@ -2056,13 +2056,13 @@
         <v>1.458</v>
       </c>
       <c r="I35" t="n">
-        <v>1.328832505473375</v>
+        <v>1.198897805881131</v>
       </c>
       <c r="J35" t="n">
         <v>0.9506666666666668</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8755585909258249</v>
+        <v>0.7448227346518818</v>
       </c>
     </row>
     <row r="36">
@@ -2091,13 +2091,13 @@
         <v>6.886</v>
       </c>
       <c r="I36" t="n">
-        <v>6.02716744684629</v>
+        <v>5.985722336758728</v>
       </c>
       <c r="J36" t="n">
         <v>1.7215</v>
       </c>
       <c r="K36" t="n">
-        <v>1.506791861711573</v>
+        <v>1.496430584189682</v>
       </c>
     </row>
   </sheetData>

--- a/01_Thermal/B_results/four_annular_gp_analysis.xlsx
+++ b/01_Thermal/B_results/four_annular_gp_analysis.xlsx
@@ -484,19 +484,19 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>32.15591478812478</v>
+        <v>29.61079149293456</v>
       </c>
       <c r="E2" t="n">
-        <v>8.662984295797726</v>
+        <v>7.676041150083327</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2027831479042894</v>
+        <v>0.1739226652479511</v>
       </c>
       <c r="G2" t="n">
-        <v>175.1958677393621</v>
+        <v>133.2232349318846</v>
       </c>
       <c r="H2" t="n">
-        <v>4260.495759386248</v>
+        <v>4404.205864527997</v>
       </c>
     </row>
     <row r="3">
@@ -512,19 +512,19 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>46.9964700435003</v>
+        <v>33.09355857163295</v>
       </c>
       <c r="E3" t="n">
-        <v>45.56542672268462</v>
+        <v>12.19682963257146</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2300603569486</v>
+        <v>0.1938661123783066</v>
       </c>
       <c r="G3" t="n">
-        <v>291.7847935990236</v>
+        <v>277.2497042747839</v>
       </c>
       <c r="H3" t="n">
-        <v>5512.886817461289</v>
+        <v>7376.787765444902</v>
       </c>
     </row>
     <row r="4">
@@ -540,19 +540,19 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>40.95357411416045</v>
+        <v>40.15002019095108</v>
       </c>
       <c r="E4" t="n">
-        <v>24.67292331395973</v>
+        <v>25.31185928737613</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2897078592162587</v>
+        <v>0.2961371082853932</v>
       </c>
       <c r="G4" t="n">
-        <v>316.1411295747739</v>
+        <v>293.3429531072492</v>
       </c>
       <c r="H4" t="n">
-        <v>3766.694924158668</v>
+        <v>3344.952825335054</v>
       </c>
     </row>
     <row r="5">
@@ -568,19 +568,19 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>39.44995219779057</v>
+        <v>39.14586614698355</v>
       </c>
       <c r="E5" t="n">
-        <v>17.5246898574569</v>
+        <v>18.51104882784288</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2835759533018062</v>
+        <v>0.232809797164752</v>
       </c>
       <c r="G5" t="n">
-        <v>1377.953541140899</v>
+        <v>1686.781042783403</v>
       </c>
       <c r="H5" t="n">
-        <v>17135.46024586531</v>
+        <v>31121.19082608325</v>
       </c>
     </row>
     <row r="6">
@@ -596,19 +596,19 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>45.37326094885551</v>
+        <v>45.81426006229779</v>
       </c>
       <c r="E6" t="n">
-        <v>24.34826070171258</v>
+        <v>25.47062316241953</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2891279587672202</v>
+        <v>0.2955108553159919</v>
       </c>
       <c r="G6" t="n">
-        <v>597.7678174596385</v>
+        <v>682.2261745354665</v>
       </c>
       <c r="H6" t="n">
-        <v>7150.76242849565</v>
+        <v>7812.346546992781</v>
       </c>
     </row>
     <row r="7">
@@ -624,19 +624,19 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>30.93351431912789</v>
+        <v>32.02574582751055</v>
       </c>
       <c r="E7" t="n">
-        <v>11.24664981384535</v>
+        <v>12.68086820589958</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2484151392453465</v>
+        <v>0.2692015255195721</v>
       </c>
       <c r="G7" t="n">
-        <v>420.0367050450863</v>
+        <v>505.9608597230443</v>
       </c>
       <c r="H7" t="n">
-        <v>6806.614016268456</v>
+        <v>6981.71133541129</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>33.91594803811211</v>
+        <v>35.61505765728622</v>
       </c>
       <c r="E8" t="n">
-        <v>11.76481362660272</v>
+        <v>12.67291566165808</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2359866003422746</v>
+        <v>0.2328597585383104</v>
       </c>
       <c r="G8" t="n">
-        <v>283.8911621744545</v>
+        <v>378.0146196540255</v>
       </c>
       <c r="H8" t="n">
-        <v>5097.734174531417</v>
+        <v>6971.395325081485</v>
       </c>
     </row>
     <row r="9">
@@ -677,19 +677,19 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>269.7786344496716</v>
+        <v>255.4552999495967</v>
       </c>
       <c r="E9" t="n">
-        <v>143.7857483320596</v>
+        <v>114.520185927851</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2638759599380512</v>
+        <v>0.2412000056873754</v>
       </c>
       <c r="G9" t="n">
-        <v>3462.771016733238</v>
+        <v>3956.798589009857</v>
       </c>
       <c r="H9" t="n">
-        <v>49730.64836616704</v>
+        <v>68012.59048887675</v>
       </c>
     </row>
   </sheetData>
@@ -793,13 +793,13 @@
         <v>7.31</v>
       </c>
       <c r="I2" t="n">
-        <v>7.416313058692195</v>
+        <v>7.262421844630803</v>
       </c>
       <c r="J2" t="n">
         <v>4.5775</v>
       </c>
       <c r="K2" t="n">
-        <v>4.856366482755949</v>
+        <v>4.690283786621561</v>
       </c>
     </row>
     <row r="3">
@@ -832,13 +832,13 @@
         <v>6.66</v>
       </c>
       <c r="I3" t="n">
-        <v>6.798336326274096</v>
+        <v>6.663950711867259</v>
       </c>
       <c r="J3" t="n">
         <v>4.343333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>4.473445021820609</v>
+        <v>4.297251612024504</v>
       </c>
     </row>
     <row r="4">
@@ -871,13 +871,13 @@
         <v>6.83</v>
       </c>
       <c r="I4" t="n">
-        <v>6.753423150299891</v>
+        <v>6.766629045556486</v>
       </c>
       <c r="J4" t="n">
         <v>4.58</v>
       </c>
       <c r="K4" t="n">
-        <v>4.615513042454795</v>
+        <v>4.619977877016016</v>
       </c>
     </row>
     <row r="5">
@@ -910,13 +910,13 @@
         <v>6.283</v>
       </c>
       <c r="I5" t="n">
-        <v>6.227028752787276</v>
+        <v>6.232966229963702</v>
       </c>
       <c r="J5" t="n">
         <v>4.354333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>4.290787507922803</v>
+        <v>4.28650199599848</v>
       </c>
     </row>
     <row r="6">
@@ -945,13 +945,13 @@
         <v>27.083</v>
       </c>
       <c r="I6" t="n">
-        <v>27.19510128805346</v>
+        <v>26.92596783201825</v>
       </c>
       <c r="J6" t="n">
         <v>6.77075</v>
       </c>
       <c r="K6" t="n">
-        <v>6.798775322013364</v>
+        <v>6.731491958004562</v>
       </c>
     </row>
     <row r="7">
@@ -984,13 +984,13 @@
         <v>3.672</v>
       </c>
       <c r="I7" t="n">
-        <v>1.323562369201061</v>
+        <v>4.276640412387382</v>
       </c>
       <c r="J7" t="n">
         <v>2.5935</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9151030632087672</v>
+        <v>2.80031568723358</v>
       </c>
     </row>
     <row r="8">
@@ -1023,13 +1023,13 @@
         <v>3.598</v>
       </c>
       <c r="I8" t="n">
-        <v>3.761384309891935</v>
+        <v>3.777747576197674</v>
       </c>
       <c r="J8" t="n">
         <v>2.582</v>
       </c>
       <c r="K8" t="n">
-        <v>2.750067219180605</v>
+        <v>2.655884321366758</v>
       </c>
     </row>
     <row r="9">
@@ -1062,13 +1062,13 @@
         <v>5.346</v>
       </c>
       <c r="I9" t="n">
-        <v>5.257965220609115</v>
+        <v>5.191660021051662</v>
       </c>
       <c r="J9" t="n">
         <v>3.14975</v>
       </c>
       <c r="K9" t="n">
-        <v>3.217130833092028</v>
+        <v>3.237974533041915</v>
       </c>
     </row>
     <row r="10">
@@ -1101,13 +1101,13 @@
         <v>3.606</v>
       </c>
       <c r="I10" t="n">
-        <v>3.648098002638617</v>
+        <v>3.634554573973266</v>
       </c>
       <c r="J10" t="n">
         <v>2.422666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>2.459096328123566</v>
+        <v>2.457184822530936</v>
       </c>
     </row>
     <row r="11">
@@ -1136,13 +1136,13 @@
         <v>16.222</v>
       </c>
       <c r="I11" t="n">
-        <v>13.99100990234073</v>
+        <v>16.88060258360998</v>
       </c>
       <c r="J11" t="n">
         <v>4.0555</v>
       </c>
       <c r="K11" t="n">
-        <v>3.497752475585183</v>
+        <v>4.220150645902496</v>
       </c>
     </row>
     <row r="12">
@@ -1175,13 +1175,13 @@
         <v>3.322</v>
       </c>
       <c r="I12" t="n">
-        <v>3.699765616822507</v>
+        <v>3.510197976209843</v>
       </c>
       <c r="J12" t="n">
         <v>1.951</v>
       </c>
       <c r="K12" t="n">
-        <v>2.128312593961923</v>
+        <v>2.043109588069425</v>
       </c>
     </row>
     <row r="13">
@@ -1214,13 +1214,13 @@
         <v>2.395</v>
       </c>
       <c r="I13" t="n">
-        <v>2.889844066610538</v>
+        <v>2.74261620423144</v>
       </c>
       <c r="J13" t="n">
         <v>1.944333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>1.963869488396502</v>
+        <v>1.892508859362436</v>
       </c>
     </row>
     <row r="14">
@@ -1253,13 +1253,13 @@
         <v>3.389</v>
       </c>
       <c r="I14" t="n">
-        <v>3.427444919494758</v>
+        <v>3.516080024994547</v>
       </c>
       <c r="J14" t="n">
         <v>2.5625</v>
       </c>
       <c r="K14" t="n">
-        <v>2.610225752755173</v>
+        <v>2.615041999425389</v>
       </c>
     </row>
     <row r="15">
@@ -1292,13 +1292,13 @@
         <v>2.734</v>
       </c>
       <c r="I15" t="n">
-        <v>2.700786222511771</v>
+        <v>2.707806827751252</v>
       </c>
       <c r="J15" t="n">
         <v>1.724</v>
       </c>
       <c r="K15" t="n">
-        <v>1.924181766351929</v>
+        <v>1.919001198772917</v>
       </c>
     </row>
     <row r="16">
@@ -1327,13 +1327,13 @@
         <v>11.84</v>
       </c>
       <c r="I16" t="n">
-        <v>12.71784082543957</v>
+        <v>12.47670103318708</v>
       </c>
       <c r="J16" t="n">
         <v>2.96</v>
       </c>
       <c r="K16" t="n">
-        <v>3.179460206359893</v>
+        <v>3.11917525829677</v>
       </c>
     </row>
     <row r="17">
@@ -1366,13 +1366,13 @@
         <v>2.997</v>
       </c>
       <c r="I17" t="n">
-        <v>1.930458679100686</v>
+        <v>1.845216697797918</v>
       </c>
       <c r="J17" t="n">
         <v>1.869</v>
       </c>
       <c r="K17" t="n">
-        <v>1.550853678705982</v>
+        <v>1.418438509795242</v>
       </c>
     </row>
     <row r="18">
@@ -1405,13 +1405,13 @@
         <v>2.182</v>
       </c>
       <c r="I18" t="n">
-        <v>2.286937626166762</v>
+        <v>2.243728583282373</v>
       </c>
       <c r="J18" t="n">
         <v>1.721</v>
       </c>
       <c r="K18" t="n">
-        <v>1.541724564113339</v>
+        <v>1.50251267440467</v>
       </c>
     </row>
     <row r="19">
@@ -1444,13 +1444,13 @@
         <v>3.611</v>
       </c>
       <c r="I19" t="n">
-        <v>3.385159081661953</v>
+        <v>3.252459065951223</v>
       </c>
       <c r="J19" t="n">
         <v>2.48</v>
       </c>
       <c r="K19" t="n">
-        <v>2.550563712863219</v>
+        <v>2.535837833854575</v>
       </c>
     </row>
     <row r="20">
@@ -1483,13 +1483,13 @@
         <v>3.509</v>
       </c>
       <c r="I20" t="n">
-        <v>3.113250383602602</v>
+        <v>3.032461437023099</v>
       </c>
       <c r="J20" t="n">
         <v>1.865</v>
       </c>
       <c r="K20" t="n">
-        <v>1.305412026478876</v>
+        <v>1.292481851172171</v>
       </c>
     </row>
     <row r="21">
@@ -1518,13 +1518,13 @@
         <v>12.299</v>
       </c>
       <c r="I21" t="n">
-        <v>10.715805770532</v>
+        <v>10.37386578405461</v>
       </c>
       <c r="J21" t="n">
         <v>3.07475</v>
       </c>
       <c r="K21" t="n">
-        <v>2.678951442633001</v>
+        <v>2.593466446013653</v>
       </c>
     </row>
     <row r="22">
@@ -1557,13 +1557,13 @@
         <v>2.954</v>
       </c>
       <c r="I22" t="n">
-        <v>2.961688890578897</v>
+        <v>2.941123486493395</v>
       </c>
       <c r="J22" t="n">
         <v>2.02725</v>
       </c>
       <c r="K22" t="n">
-        <v>2.356474878304748</v>
+        <v>2.363427234342201</v>
       </c>
     </row>
     <row r="23">
@@ -1596,13 +1596,13 @@
         <v>2.144</v>
       </c>
       <c r="I23" t="n">
-        <v>2.286964638287909</v>
+        <v>2.418840042986725</v>
       </c>
       <c r="J23" t="n">
         <v>1.503666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>1.771202297030148</v>
+        <v>1.834562837050476</v>
       </c>
     </row>
     <row r="24">
@@ -1635,13 +1635,13 @@
         <v>1.642</v>
       </c>
       <c r="I24" t="n">
-        <v>1.953045172332649</v>
+        <v>2.036429048358384</v>
       </c>
       <c r="J24" t="n">
         <v>1.25525</v>
       </c>
       <c r="K24" t="n">
-        <v>1.27316742326134</v>
+        <v>1.279541838328937</v>
       </c>
     </row>
     <row r="25">
@@ -1674,13 +1674,13 @@
         <v>2.317</v>
       </c>
       <c r="I25" t="n">
-        <v>2.337749728686704</v>
+        <v>2.307252486341163</v>
       </c>
       <c r="J25" t="n">
         <v>1.458</v>
       </c>
       <c r="K25" t="n">
-        <v>1.713087421550177</v>
+        <v>1.715852888649882</v>
       </c>
     </row>
     <row r="26">
@@ -1709,13 +1709,13 @@
         <v>9.057</v>
       </c>
       <c r="I26" t="n">
-        <v>9.539448429886159</v>
+        <v>9.703645064179668</v>
       </c>
       <c r="J26" t="n">
         <v>2.26425</v>
       </c>
       <c r="K26" t="n">
-        <v>2.38486210747154</v>
+        <v>2.425911266044917</v>
       </c>
     </row>
     <row r="27">
@@ -1748,13 +1748,13 @@
         <v>2.598</v>
       </c>
       <c r="I27" t="n">
-        <v>2.350909118958581</v>
+        <v>2.21628856712421</v>
       </c>
       <c r="J27" t="n">
         <v>1.5755</v>
       </c>
       <c r="K27" t="n">
-        <v>1.538046333577959</v>
+        <v>1.501643050740533</v>
       </c>
     </row>
     <row r="28">
@@ -1787,13 +1787,13 @@
         <v>1.464</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9341557894611</v>
+        <v>2.046963487917811</v>
       </c>
       <c r="J28" t="n">
         <v>1.202666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>1.682781915305274</v>
+        <v>1.714867176133942</v>
       </c>
     </row>
     <row r="29">
@@ -1826,13 +1826,13 @@
         <v>1.402</v>
       </c>
       <c r="I29" t="n">
-        <v>1.527779455398029</v>
+        <v>1.589093685298639</v>
       </c>
       <c r="J29" t="n">
         <v>1.1765</v>
       </c>
       <c r="K29" t="n">
-        <v>1.264480872067553</v>
+        <v>1.276782935770268</v>
       </c>
     </row>
     <row r="30">
@@ -1865,13 +1865,13 @@
         <v>2.042</v>
       </c>
       <c r="I30" t="n">
-        <v>1.780429802997515</v>
+        <v>1.773135831510515</v>
       </c>
       <c r="J30" t="n">
         <v>1.508666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>1.17926914763693</v>
+        <v>1.182983620623201</v>
       </c>
     </row>
     <row r="31">
@@ -1900,13 +1900,13 @@
         <v>7.505999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>7.593274166815225</v>
+        <v>7.625481571851176</v>
       </c>
       <c r="J31" t="n">
         <v>1.8765</v>
       </c>
       <c r="K31" t="n">
-        <v>1.898318541703806</v>
+        <v>1.906370392962794</v>
       </c>
     </row>
     <row r="32">
@@ -1939,13 +1939,13 @@
         <v>2.347</v>
       </c>
       <c r="I32" t="n">
-        <v>1.613707493165421</v>
+        <v>1.665934357401471</v>
       </c>
       <c r="J32" t="n">
         <v>1.196</v>
       </c>
       <c r="K32" t="n">
-        <v>1.210334758106222</v>
+        <v>1.227424225014528</v>
       </c>
     </row>
     <row r="33">
@@ -1978,13 +1978,13 @@
         <v>1.6</v>
       </c>
       <c r="I33" t="n">
-        <v>1.490481394676311</v>
+        <v>1.540673138099821</v>
       </c>
       <c r="J33" t="n">
         <v>0.8406666666666668</v>
       </c>
       <c r="K33" t="n">
-        <v>1.069196562412963</v>
+        <v>1.110276895484575</v>
       </c>
     </row>
     <row r="34">
@@ -2017,13 +2017,13 @@
         <v>1.481</v>
       </c>
       <c r="I34" t="n">
-        <v>1.682635643035865</v>
+        <v>1.693364043978105</v>
       </c>
       <c r="J34" t="n">
         <v>0.7117500000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9073546471057639</v>
+        <v>0.8925296023198701</v>
       </c>
     </row>
     <row r="35">
@@ -2056,13 +2056,13 @@
         <v>1.458</v>
       </c>
       <c r="I35" t="n">
-        <v>1.198897805881131</v>
+        <v>1.206153192889763</v>
       </c>
       <c r="J35" t="n">
         <v>0.9506666666666668</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7448227346518818</v>
+        <v>0.7597761877716707</v>
       </c>
     </row>
     <row r="36">
@@ -2091,13 +2091,13 @@
         <v>6.886</v>
       </c>
       <c r="I36" t="n">
-        <v>5.985722336758728</v>
+        <v>6.10612473236916</v>
       </c>
       <c r="J36" t="n">
         <v>1.7215</v>
       </c>
       <c r="K36" t="n">
-        <v>1.496430584189682</v>
+        <v>1.52653118309229</v>
       </c>
     </row>
   </sheetData>
